--- a/outputs/43436.xlsx
+++ b/outputs/43436.xlsx
@@ -163,43 +163,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -430,7 +430,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.56"/>
@@ -488,15 +488,15 @@
         <v>1</v>
       </c>
       <c r="I2" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G2,C:C,"&lt;="&amp;DATE(2022,5,31))-COUNTIFS(B:B,$G2,C:C,"&lt;="&amp;DATE(2022,5,31),D:D,"&lt;"&amp;DATE(2022,5,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G2)*($C$2:$C$12&lt;=DATE(2022,5,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,5,1))))</f>
         <v>1</v>
       </c>
       <c r="J2" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G2,C:C,"&lt;="&amp;DATE(2022,6,30))-COUNTIFS(B:B,$G2,C:C,"&lt;="&amp;DATE(2022,6,30),D:D,"&lt;"&amp;DATE(2022,6,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G2)*($C$2:$C$12&lt;=DATE(2022,6,30))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,6,1))))</f>
         <v>2</v>
       </c>
       <c r="K2" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G2,C:C,"&lt;="&amp;DATE(2022,7,31))-COUNTIFS(B:B,$G2,C:C,"&lt;="&amp;DATE(2022,7,31),D:D,"&lt;"&amp;DATE(2022,7,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G2)*($C$2:$C$12&lt;=DATE(2022,7,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,7,1))))</f>
         <v>2</v>
       </c>
     </row>
@@ -521,15 +521,15 @@
         <v>2</v>
       </c>
       <c r="I3" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G3,C:C,"&lt;="&amp;DATE(2022,5,31))-COUNTIFS(B:B,$G3,C:C,"&lt;="&amp;DATE(2022,5,31),D:D,"&lt;"&amp;DATE(2022,5,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G3)*($C$2:$C$12&lt;=DATE(2022,5,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,5,1))))</f>
         <v>4</v>
       </c>
       <c r="J3" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G3,C:C,"&lt;="&amp;DATE(2022,6,30))-COUNTIFS(B:B,$G3,C:C,"&lt;="&amp;DATE(2022,6,30),D:D,"&lt;"&amp;DATE(2022,6,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G3)*($C$2:$C$12&lt;=DATE(2022,6,30))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,6,1))))</f>
         <v>4</v>
       </c>
       <c r="K3" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G3,C:C,"&lt;="&amp;DATE(2022,7,31))-COUNTIFS(B:B,$G3,C:C,"&lt;="&amp;DATE(2022,7,31),D:D,"&lt;"&amp;DATE(2022,7,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G3)*($C$2:$C$12&lt;=DATE(2022,7,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,7,1))))</f>
         <v>4</v>
       </c>
     </row>
@@ -554,15 +554,15 @@
         <v>1</v>
       </c>
       <c r="I4" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G4,C:C,"&lt;="&amp;DATE(2022,5,31))-COUNTIFS(B:B,$G4,C:C,"&lt;="&amp;DATE(2022,5,31),D:D,"&lt;"&amp;DATE(2022,5,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G4)*($C$2:$C$12&lt;=DATE(2022,5,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,5,1))))</f>
         <v>2</v>
       </c>
       <c r="J4" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G4,C:C,"&lt;="&amp;DATE(2022,6,30))-COUNTIFS(B:B,$G4,C:C,"&lt;="&amp;DATE(2022,6,30),D:D,"&lt;"&amp;DATE(2022,6,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G4)*($C$2:$C$12&lt;=DATE(2022,6,30))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,6,1))))</f>
         <v>2</v>
       </c>
       <c r="K4" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G4,C:C,"&lt;="&amp;DATE(2022,7,31))-COUNTIFS(B:B,$G4,C:C,"&lt;="&amp;DATE(2022,7,31),D:D,"&lt;"&amp;DATE(2022,7,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G4)*($C$2:$C$12&lt;=DATE(2022,7,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,7,1))))</f>
         <v>2</v>
       </c>
     </row>
@@ -585,15 +585,15 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G5,C:C,"&lt;="&amp;DATE(2022,5,31))-COUNTIFS(B:B,$G5,C:C,"&lt;="&amp;DATE(2022,5,31),D:D,"&lt;"&amp;DATE(2022,5,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G5)*($C$2:$C$12&lt;=DATE(2022,5,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,5,1))))</f>
         <v>1</v>
       </c>
       <c r="J5" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G5,C:C,"&lt;="&amp;DATE(2022,6,30))-COUNTIFS(B:B,$G5,C:C,"&lt;="&amp;DATE(2022,6,30),D:D,"&lt;"&amp;DATE(2022,6,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G5)*($C$2:$C$12&lt;=DATE(2022,6,30))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,6,1))))</f>
         <v>0</v>
       </c>
       <c r="K5" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G5,C:C,"&lt;="&amp;DATE(2022,7,31))-COUNTIFS(B:B,$G5,C:C,"&lt;="&amp;DATE(2022,7,31),D:D,"&lt;"&amp;DATE(2022,7,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G5)*($C$2:$C$12&lt;=DATE(2022,7,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,7,1))))</f>
         <v>0</v>
       </c>
     </row>
@@ -616,15 +616,15 @@
         <v>1</v>
       </c>
       <c r="I6" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G6,C:C,"&lt;="&amp;DATE(2022,5,31))-COUNTIFS(B:B,$G6,C:C,"&lt;="&amp;DATE(2022,5,31),D:D,"&lt;"&amp;DATE(2022,5,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G6)*($C$2:$C$12&lt;=DATE(2022,5,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,5,1))))</f>
         <v>0</v>
       </c>
       <c r="J6" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G6,C:C,"&lt;="&amp;DATE(2022,6,30))-COUNTIFS(B:B,$G6,C:C,"&lt;="&amp;DATE(2022,6,30),D:D,"&lt;"&amp;DATE(2022,6,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G6)*($C$2:$C$12&lt;=DATE(2022,6,30))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,6,1))))</f>
         <v>0</v>
       </c>
       <c r="K6" s="7" t="n">
-        <f aca="false">COUNTIFS(B:B,$G6,C:C,"&lt;="&amp;DATE(2022,7,31))-COUNTIFS(B:B,$G6,C:C,"&lt;="&amp;DATE(2022,7,31),D:D,"&lt;"&amp;DATE(2022,7,1))</f>
+        <f aca="false">SUMPRODUCT(($B$2:$B$12=G6)*($C$2:$C$12&lt;=DATE(2022,7,31))*(($D$2:$D$12="")+($D$2:$D$12&gt;=DATE(2022,7,1))))</f>
         <v>1</v>
       </c>
     </row>
